--- a/resampling/input/accessibility_reports_returned/Solidarités_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_returned/Solidarités_accessibility_report.xlsx
@@ -18,7 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd-mmm-yyyy"/>
+  </numFmts>
   <fonts count="8">
     <font>
       <name val="Calibri"/>
@@ -140,7 +142,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -169,6 +171,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -246,7 +249,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WardAccessibility" displayName="WardAccessibility" ref="A1:Q24" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WardAccessibility" displayName="WardAccessibility" ref="A1:Q26" headerRowCount="1">
   <autoFilter ref="A1:Q24"/>
   <tableColumns count="17">
     <tableColumn id="1" name="State"/>
@@ -1693,7 +1696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q24"/>
+  <dimension ref="A1:Q26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="17" min="1" max="1"/>
@@ -1832,8 +1835,16 @@
       <c r="J2" t="n">
         <v>13</v>
       </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1865,8 +1876,21 @@
       <c r="J3" t="n">
         <v>12</v>
       </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>partner marked inaccessible but did not provide a reason category on return - follow up needed</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1898,8 +1922,16 @@
       <c r="J4" t="n">
         <v>12</v>
       </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1931,8 +1963,16 @@
       <c r="J5" t="n">
         <v>12</v>
       </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1964,8 +2004,16 @@
       <c r="J6" t="n">
         <v>10</v>
       </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1997,8 +2045,21 @@
       <c r="J7" t="n">
         <v>8</v>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>partner marked inaccessible but did not provide a reason category on return - follow up needed</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2030,8 +2091,16 @@
       <c r="J8" t="n">
         <v>8</v>
       </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2063,8 +2132,16 @@
       <c r="J9" t="n">
         <v>6</v>
       </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2096,8 +2173,16 @@
       <c r="J10" t="n">
         <v>6</v>
       </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2129,8 +2214,16 @@
       <c r="J11" t="n">
         <v>6</v>
       </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2162,8 +2255,16 @@
       <c r="J12" t="n">
         <v>6</v>
       </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2195,8 +2296,16 @@
       <c r="J13" t="n">
         <v>3</v>
       </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2238,8 +2347,16 @@
       <c r="J14" t="n">
         <v>82</v>
       </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2271,8 +2388,16 @@
       <c r="J15" t="n">
         <v>33</v>
       </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2304,8 +2429,21 @@
       <c r="J16" t="n">
         <v>18</v>
       </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>partner marked inaccessible but did not provide a reason category on return - follow up needed</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2337,8 +2475,21 @@
       <c r="J17" t="n">
         <v>18</v>
       </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>partner marked inaccessible but did not provide a reason category on return - follow up needed</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2370,8 +2521,21 @@
       <c r="J18" t="n">
         <v>11</v>
       </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>partner marked inaccessible but did not provide a reason category on return - follow up needed</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2403,8 +2567,21 @@
       <c r="J19" t="n">
         <v>10</v>
       </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>partner marked inaccessible but did not provide a reason category on return - follow up needed</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2492,8 +2669,16 @@
       <c r="J21" t="n">
         <v>9</v>
       </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2535,8 +2720,21 @@
       <c r="J22" t="n">
         <v>6</v>
       </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>partner marked inaccessible but did not provide a reason category on return - follow up needed</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2568,8 +2766,21 @@
       <c r="J23" t="n">
         <v>4</v>
       </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>partner marked inaccessible but did not provide a reason category on return - follow up needed</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2601,22 +2812,125 @@
       <c r="J24" t="n">
         <v>4</v>
       </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>partner marked inaccessible but did not provide a reason category on return - follow up needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Anka</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Dakko</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Bakura</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-16 - not previously listed. This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>10</v>
+      </c>
+      <c r="O25" s="20" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Anka</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ruwan Gizo</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Talata Mafara</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-16 - not previously listed. This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>8</v>
+      </c>
+      <c r="O26" s="20" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="4">
-    <dataValidation sqref="K2:K24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <dataValidations count="5">
+    <dataValidation sqref="K2:K24 K25:K26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="L2:L24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L2:L24 L25:L26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N/A - fully accessible,Insecurity / conflict,Physical access (terrain, flooding, roads),Population absent / relocated,Building-footprint issue (no eligible structures),Access denied by authorities / community,Other"</formula1>
     </dataValidation>
-    <dataValidation sqref="P2:P24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P2:P24 P25:P26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner,IMPACT (default - accessible until reported otherwise)"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q2:Q24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Q2:Q24 Q25:Q26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner's own template,Email,WhatsApp/verbal (coordinator-transcribed),Point-level file annotation,N/A"</formula1>
+    </dataValidation>
+    <dataValidation sqref="O25:O26" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today." type="date" operator="between">
+      <formula1>2026-07-01</formula1>
+      <formula2>2026-09-16</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2765,8 +3079,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2804,8 +3116,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2843,8 +3153,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2882,8 +3190,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2921,8 +3227,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2960,8 +3264,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2999,8 +3301,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3038,8 +3338,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3077,8 +3375,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3116,8 +3412,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3155,8 +3449,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3194,8 +3486,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3233,8 +3523,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3272,8 +3560,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3311,8 +3597,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3350,8 +3634,6 @@
           <t>12</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4639,13 +4921,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84C0D273-EEDB-4B24-B8C5-8E07BD30A1B7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E166913-D85B-4238-A4E4-2E98699EBCDD}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{68EFE501-9B15-444F-B75B-82151AE2B7E1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72310A83-70D2-4FBB-82F1-696644D8789E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EAD2D42-235C-4440-BD94-0F5131CAB467}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50262B3E-4E71-45D7-AD15-01A67DCEE0A5}"/>
 </file>
--- a/resampling/input/accessibility_reports_returned/Solidarités_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_returned/Solidarités_accessibility_report.xlsx
@@ -249,8 +249,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WardAccessibility" displayName="WardAccessibility" ref="A1:Q26" headerRowCount="1">
-  <autoFilter ref="A1:Q24"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WardAccessibility" displayName="WardAccessibility" ref="A1:Q48" headerRowCount="1">
+  <autoFilter ref="A1:Q48"/>
   <tableColumns count="17">
     <tableColumn id="1" name="State"/>
     <tableColumn id="2" name="LGA"/>
@@ -1696,7 +1696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q26"/>
+  <dimension ref="A1:Q48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="17" min="1" max="1"/>
@@ -2844,7 +2844,6 @@
           <t>Dakko</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2887,7 +2886,6 @@
           <t>Ruwan Gizo</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2914,23 +2912,912 @@
       </c>
       <c r="O26" s="20" t="n"/>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Kebbi</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Gwandu</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Alwasa</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Argungu; Birnin Kebbi</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Kebbi</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Gwandu</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Dogon Daji</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Kebbi</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Gwandu</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Felande</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Argungu</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Kebbi</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Gwandu</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Gwazange</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Argungu</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Kebbi</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Gwandu</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Jiga Birni</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Aleiro</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Kebbi</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Gwandu</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Kashin Zama</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Aleiro</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Kebbi</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Gwandu</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Aleiro; Birnin Kebbi</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Kebbi</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Gwandu</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Saida Goshe</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Argungu; Augie</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Kebbi</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Gwandu</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Sanyinnawal</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Kebbi</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Gwandu</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Tambuwal</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Kebbi</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Gwandu</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ujariyo</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Argungu; Birnin Kebbi</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Anka</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Bindin</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Bungudu; Maru</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Anka</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Damri</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Bakura; Talata Mafara</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Anka</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Dangulbi</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Bukkuyum; Maru</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Anka</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Dankurmi</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Bukkuyum; Maru</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Anka</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Gwaram</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Maru; Talata Mafara</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Anka</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Jangebe</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Talata Mafara</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Anka</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Kanoma</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Bungudu; Maru; Talata Mafara</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Anka</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Nasarawa</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Bakura; Bukkuyum</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Anka</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ruwan Jema</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Bakura; Bukkuyum</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Anka</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Sauna Ruwan Gora</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Bakura; Talata Mafara</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Anka</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Yashi</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Bukkuyum</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation sqref="K2:K24 K25:K26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="L2:L24 L25:L26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L2:L48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N/A - fully accessible,Insecurity / conflict,Physical access (terrain, flooding, roads),Population absent / relocated,Building-footprint issue (no eligible structures),Access denied by authorities / community,Other"</formula1>
     </dataValidation>
-    <dataValidation sqref="P2:P24 P25:P26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P2:P48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner,IMPACT (default - accessible until reported otherwise)"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q2:Q24 Q25:Q26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Q2:Q48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner's own template,Email,WhatsApp/verbal (coordinator-transcribed),Point-level file annotation,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="O25:O26" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today." type="date" operator="between">
+    <dataValidation sqref="O2:O48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date">
       <formula1>2026-07-01</formula1>
-      <formula2>2026-09-16</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4666,8 +5553,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010064B5BF8B0F90A143B1A4ACAD04008153" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada0274d0d067bbbdece3301958c05ce">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="30973102-2308-455b-8e1f-b6a90edc3b23" xmlns:ns3="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1f05eaaac1f596f0cf4554f8e9f637ce" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010064B5BF8B0F90A143B1A4ACAD04008153" ma:contentTypeVersion="15" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="7a2915931200ea69f6d4702d545d15c4">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="30973102-2308-455b-8e1f-b6a90edc3b23" xmlns:ns3="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ebf5164e0bbea30cbcbeb97056918f83" ns2:_="" ns3:_="">
     <xsd:import namespace="30973102-2308-455b-8e1f-b6a90edc3b23"/>
     <xsd:import namespace="947c1918-d5ab-48a1-8b61-0d52f2f99fd1"/>
     <xsd:element name="properties">
@@ -4715,7 +5602,7 @@
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="12" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4d06f0b5-5743-41f2-90d3-b12c8ffc7f36" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="12" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Balises d’images" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4d06f0b5-5743-41f2-90d3-b12c8ffc7f36" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -4774,7 +5661,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Partagé avec" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -4793,7 +5680,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Partagé avec détails" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -4810,8 +5697,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Type de contenu"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Titre"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -4921,13 +5808,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E166913-D85B-4238-A4E4-2E98699EBCDD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5899227-125F-48A3-A23C-627E4096655F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72310A83-70D2-4FBB-82F1-696644D8789E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ADA007F3-7BD6-47AB-8558-FC23204C7783}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50262B3E-4E71-45D7-AD15-01A67DCEE0A5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3C7F112-D52B-4F79-B536-C531389CE90D}"/>
 </file>
--- a/resampling/input/accessibility_reports_returned/Solidarités_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_returned/Solidarités_accessibility_report.xlsx
@@ -275,8 +275,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:O36" headerRowCount="1">
-  <autoFilter ref="A1:O36"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:O54" headerRowCount="1">
+  <autoFilter ref="A1:O54"/>
   <tableColumns count="15">
     <tableColumn id="1" name="State"/>
     <tableColumn id="2" name="LGA"/>
@@ -2974,7 +2974,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -3257,7 +3256,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -3294,7 +3292,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -3833,7 +3830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O36"/>
+  <dimension ref="A1:O54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="17" min="1" max="1"/>
@@ -5530,18 +5527,726 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Anka</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Dakko</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>non_idp_NG037001_supp2</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Kebbi</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Gwandu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Dodoru</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>non_idp_NG022010_supp1</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Kebbi</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Gwandu</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Maruda</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>non_idp_NG022010_supp2</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Kebbi</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Gwandu</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Dalijan</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>non_idp_NG022010_supp3</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Anka</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Dakko</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>non_idp_NG037001_supp11</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Anka</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Galadima</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>non_idp_NG037001_supp12</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Anka</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Magaji</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>non_idp_NG037001_supp13</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Anka</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Magaji</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>non_idp_NG037001_supp14</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Anka</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Galadima</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>non_idp_NG037001_supp16</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Anka</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Galadima</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>non_idp_NG037001_supp17</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Anka</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ruwan Gizo</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>non_idp_NG037001_supp18</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Anka</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Galadima</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>non_idp_NG037001_supp19</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Anka</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Magaji</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>idp_NG037001_supp1</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>In-camp</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Anka</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Magaji</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>idp_NG037001_supp2</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>In-camp</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Anka</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Magaji</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>idp_NG037001_supp3</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>In-camp</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Anka</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Magaji</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>idp_NG037001_supp4</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>In-camp</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Anka</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Magaji</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>idp_NG037001_supp5</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>In-camp</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Anka</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Dangaladima</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>idp_NG037001_supp6</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>In-camp</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation sqref="I2:I36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N/A - fully accessible,Insecurity / conflict,Physical access (terrain, flooding, roads),Population absent / relocated,Building-footprint issue (no eligible structures),Access denied by authorities / community,Other"</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N2:N54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner,IMPACT (default - accessible until reported otherwise)"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O2:O54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner's own template,Email,WhatsApp/verbal (coordinator-transcribed),Point-level file annotation,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5553,8 +6258,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010064B5BF8B0F90A143B1A4ACAD04008153" ma:contentTypeVersion="15" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="7a2915931200ea69f6d4702d545d15c4">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="30973102-2308-455b-8e1f-b6a90edc3b23" xmlns:ns3="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ebf5164e0bbea30cbcbeb97056918f83" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010064B5BF8B0F90A143B1A4ACAD04008153" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada0274d0d067bbbdece3301958c05ce">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="30973102-2308-455b-8e1f-b6a90edc3b23" xmlns:ns3="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1f05eaaac1f596f0cf4554f8e9f637ce" ns2:_="" ns3:_="">
     <xsd:import namespace="30973102-2308-455b-8e1f-b6a90edc3b23"/>
     <xsd:import namespace="947c1918-d5ab-48a1-8b61-0d52f2f99fd1"/>
     <xsd:element name="properties">
@@ -5602,7 +6307,7 @@
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="12" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Balises d’images" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4d06f0b5-5743-41f2-90d3-b12c8ffc7f36" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="12" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4d06f0b5-5743-41f2-90d3-b12c8ffc7f36" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -5661,7 +6366,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Partagé avec" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -5680,7 +6385,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Partagé avec détails" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -5697,8 +6402,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Type de contenu"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Titre"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -5808,13 +6513,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5899227-125F-48A3-A23C-627E4096655F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{96281E81-7E66-4F60-9DFE-1310664E622E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ADA007F3-7BD6-47AB-8558-FC23204C7783}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D90509C-62A6-4B09-974E-7969AC48DB4C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3C7F112-D52B-4F79-B536-C531389CE90D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AB7EC90-431E-448C-8DD0-90738797225C}"/>
 </file>
--- a/resampling/input/accessibility_reports_returned/Solidarités_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_returned/Solidarités_accessibility_report.xlsx
@@ -6255,271 +6255,4 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010064B5BF8B0F90A143B1A4ACAD04008153" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada0274d0d067bbbdece3301958c05ce">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="30973102-2308-455b-8e1f-b6a90edc3b23" xmlns:ns3="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1f05eaaac1f596f0cf4554f8e9f637ce" ns2:_="" ns3:_="">
-    <xsd:import namespace="30973102-2308-455b-8e1f-b6a90edc3b23"/>
-    <xsd:import namespace="947c1918-d5ab-48a1-8b61-0d52f2f99fd1"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="30973102-2308-455b-8e1f-b6a90edc3b23" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="12" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4d06f0b5-5743-41f2-90d3-b12c8ffc7f36" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="14" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="18" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="21" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="22" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="13" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{daf5bdda-bc47-491d-9935-b3e42d5c0ae4}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="947c1918-d5ab-48a1-8b61-0d52f2f99fd1">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="30973102-2308-455b-8e1f-b6a90edc3b23">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{96281E81-7E66-4F60-9DFE-1310664E622E}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D90509C-62A6-4B09-974E-7969AC48DB4C}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AB7EC90-431E-448C-8DD0-90738797225C}"/>
 </file>
--- a/resampling/input/accessibility_reports_returned/Solidarités_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_returned/Solidarités_accessibility_report.xlsx
@@ -6255,4 +6255,271 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010064B5BF8B0F90A143B1A4ACAD04008153" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada0274d0d067bbbdece3301958c05ce">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="30973102-2308-455b-8e1f-b6a90edc3b23" xmlns:ns3="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1f05eaaac1f596f0cf4554f8e9f637ce" ns2:_="" ns3:_="">
+    <xsd:import namespace="30973102-2308-455b-8e1f-b6a90edc3b23"/>
+    <xsd:import namespace="947c1918-d5ab-48a1-8b61-0d52f2f99fd1"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="30973102-2308-455b-8e1f-b6a90edc3b23" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="12" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4d06f0b5-5743-41f2-90d3-b12c8ffc7f36" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="14" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="18" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="21" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="22" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="13" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{daf5bdda-bc47-491d-9935-b3e42d5c0ae4}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="947c1918-d5ab-48a1-8b61-0d52f2f99fd1">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="30973102-2308-455b-8e1f-b6a90edc3b23">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{507F3159-F46E-4A03-88D4-2FCD57667413}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FAE07473-6740-4E0D-9B0D-10FBFB9D0282}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14BEB650-932C-4833-8941-4EFB565DC484}"/>
 </file>